--- a/北部山头3940平台2026/7、单日数据/北部山头3940平台-1003/二次圈矿成果_auto/3940平台 1003炮孔数据报告.xlsx
+++ b/北部山头3940平台2026/7、单日数据/北部山头3940平台-1003/二次圈矿成果_auto/3940平台 1003炮孔数据报告.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,23 +514,23 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>3.000-999.000</t>
+          <t>1.500-3.000</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>14.8</v>
+        <v>6861.985</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.96</v>
+        <v>18527.359</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4.27</v>
+        <v>2.101</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.706</v>
+        <v>389.336</v>
       </c>
     </row>
     <row r="4">
@@ -541,299 +541,171 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n">
-        <v>14.8</v>
+        <v>6861.985</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>39.96</v>
+        <v>18527.359</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4.27</v>
+        <v>2.101</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.706</v>
+        <v>389.336</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.500-3.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5655.988</v>
+        <v>2337.028</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>15271.168</v>
+        <v>6309.976</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.048</v>
+        <v>1.099</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>312.816</v>
+        <v>69.34</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1.000-1.500</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>861.396</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2325.768</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>26.591</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>5655.988</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>15271.168</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2.048</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>312.816</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>1.000-1.500</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1621.904</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4379.14</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1.157</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>50.673</v>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>3198.424</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>8635.744000000001</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>95.931</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>1.000-1.500</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>661.909</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>1787.155</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1.365</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>24.395</v>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>10060.408</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>27163.103</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>485.266</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>1.000-1.500</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>9.932</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>26.818</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.346</v>
-      </c>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>2293.745</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>6193.112</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1.218</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>75.414</v>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>炮孔品位统计（孔数）</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>≥3</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>260.805</v>
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>1.5-3</t>
+        </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>704.174</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.76</v>
+        <v>23</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>1-1.5</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5.352</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>0.5-1</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>256.945</v>
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>&lt;0.5</t>
+        </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>693.752</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>合计孔数</t>
+        </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4.856</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>517.75</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1397.926</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>10.208</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n">
-        <v>8482.284</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>22902.166</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>1.747</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>400.144</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>炮孔品位统计（孔数）</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>≥3</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>1.5-3</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>1-1.5</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>0.5-1</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>&lt;0.5</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>合计孔数</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
         <v>38</v>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/北部山头3940平台-1003/二次圈矿成果_auto/3940平台 1003炮孔数据报告.xlsx
+++ b/北部山头3940平台2026/7、单日数据/北部山头3940平台-1003/二次圈矿成果_auto/3940平台 1003炮孔数据报告.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -521,16 +521,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6861.985</v>
+        <v>7024.218</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>18527.359</v>
+        <v>18965.39</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2.101</v>
+        <v>2.004</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>389.336</v>
+        <v>380.034</v>
       </c>
     </row>
     <row r="4">
@@ -541,16 +541,16 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="7" t="n">
-        <v>6861.985</v>
+        <v>7024.218</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>18527.359</v>
+        <v>18965.39</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2.101</v>
+        <v>2.004</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>389.336</v>
+        <v>380.034</v>
       </c>
     </row>
     <row r="5">
@@ -563,82 +563,72 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2337.028</v>
+        <v>2352.433</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6309.976</v>
+        <v>6351.57</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1.099</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>69.34</v>
+        <v>69.797</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>1.000-1.500</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>861.396</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>2325.768</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>26.591</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>2352.433</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>6351.57</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>69.797</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>3198.424</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>8635.744000000001</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>95.931</v>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>9376.652</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>25316.959</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>449.83</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n">
-        <v>10060.408</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>27163.103</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>485.266</v>
-      </c>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>炮孔品位统计（孔数）</t>
+        </is>
+      </c>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -646,66 +636,54 @@
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>炮孔品位统计（孔数）</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>≥3</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>1.5-3</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>1-1.5</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>≥3</t>
+          <t>0.5-1</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>1.5-3</t>
+          <t>&lt;0.5</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1-1.5</t>
+          <t>合计孔数</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>0.5-1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>&lt;0.5</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>合计孔数</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
         <v>38</v>
       </c>
     </row>
